--- a/Excel/PublicQiangHuaConfig.xlsx
+++ b/Excel/PublicQiangHuaConfig.xlsx
@@ -1,39 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0BF220-D431-416F-88F6-88655FAF4B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="EquipQiangHuaProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Admin</author>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -42,7 +48,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -51,14 +56,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="N3" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者</t>
@@ -68,7 +72,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>:
 10.</t>
@@ -78,7 +82,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">生命值
@@ -89,7 +92,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>11.</t>
         </r>
@@ -98,7 +101,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>物理攻击</t>
@@ -108,7 +110,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">       
 14.</t>
@@ -118,7 +120,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">魔法攻击
@@ -129,7 +130,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>17.</t>
         </r>
@@ -138,7 +139,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>物理防御</t>
@@ -148,7 +148,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">        
 20.</t>
@@ -158,7 +158,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">魔法防御
@@ -169,7 +168,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>30.</t>
         </r>
@@ -178,7 +177,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">暴击
@@ -189,7 +187,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>31.</t>
         </r>
@@ -198,7 +196,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">命中
@@ -209,7 +206,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>32.</t>
         </r>
@@ -218,7 +215,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">闪避
@@ -229,7 +225,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>33.</t>
         </r>
@@ -238,7 +234,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">物理免伤
@@ -249,7 +244,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>34.</t>
         </r>
@@ -258,7 +253,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">魔法免伤
@@ -269,7 +263,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>35.</t>
         </r>
@@ -278,7 +272,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">移动速度
@@ -289,7 +282,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>36.</t>
         </r>
@@ -298,7 +291,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">伤害减免
@@ -309,7 +301,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>50:</t>
         </r>
@@ -318,7 +310,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">血量百分比
@@ -329,7 +320,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>51</t>
         </r>
@@ -338,7 +329,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：物攻百分比
@@ -349,7 +339,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>52</t>
         </r>
@@ -358,7 +348,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：魔攻百分比
@@ -369,7 +358,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>53</t>
         </r>
@@ -378,7 +367,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：物防百分比
@@ -389,7 +377,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>54</t>
         </r>
@@ -398,7 +386,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：魔防百分比
@@ -409,7 +396,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>101</t>
         </r>
@@ -418,7 +405,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：格挡值
@@ -429,7 +415,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>111</t>
         </r>
@@ -438,7 +424,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：重击概率
@@ -449,7 +434,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">112:  </t>
         </r>
@@ -458,7 +443,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">重击附加伤害值
@@ -469,7 +453,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">121:  </t>
         </r>
@@ -478,7 +462,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">每次普通攻击附加的伤害值
@@ -489,7 +472,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">131:  </t>
         </r>
@@ -498,7 +481,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>忽视目标防御值</t>
@@ -508,7 +490,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">   
 132:  </t>
@@ -518,7 +500,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">忽视目标魔防值
@@ -529,7 +510,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">133:  </t>
         </r>
@@ -538,7 +519,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">忽视目标百分比防御值
@@ -549,7 +529,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">134:  </t>
         </r>
@@ -558,7 +538,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">忽视目标百分比魔防值
@@ -569,7 +548,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">141:  </t>
         </r>
@@ -578,7 +557,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">吸血概率
@@ -589,7 +567,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">151:  </t>
         </r>
@@ -598,7 +576,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">法术反击
@@ -609,7 +586,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">152:  </t>
         </r>
@@ -618,7 +595,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">攻击反击
@@ -629,7 +605,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>161</t>
         </r>
@@ -638,7 +614,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：韧性
@@ -649,7 +624,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>201</t>
         </r>
@@ -658,7 +633,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：初始暴击等级
@@ -669,7 +643,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>202</t>
         </r>
@@ -678,7 +652,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：初始韧性等级
@@ -689,7 +662,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>203</t>
         </r>
@@ -698,7 +671,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：初始命中等级
@@ -709,7 +681,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>204</t>
         </r>
@@ -718,7 +690,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：初始闪避等级
@@ -729,7 +700,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>301:</t>
         </r>
@@ -738,7 +709,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">光抗性
@@ -749,7 +719,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>302:</t>
         </r>
@@ -758,7 +728,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">暗抗性
@@ -769,7 +738,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>303:</t>
         </r>
@@ -778,7 +747,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">火抗性
@@ -789,7 +757,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>304:</t>
         </r>
@@ -798,7 +766,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">水抗性
@@ -809,7 +776,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>305:</t>
         </r>
@@ -818,7 +785,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">电抗性
@@ -829,7 +795,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>321</t>
         </r>
@@ -838,7 +804,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -848,7 +813,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//</t>
         </r>
@@ -857,7 +822,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">野兽攻击抗性
@@ -868,7 +832,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>322</t>
         </r>
@@ -877,7 +841,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -887,7 +850,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//</t>
         </r>
@@ -896,7 +859,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">人物攻击抗性
@@ -907,7 +869,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>323</t>
         </r>
@@ -916,7 +878,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -926,7 +887,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//</t>
         </r>
@@ -935,7 +896,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">恶魔攻击抗性
@@ -946,7 +906,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>401</t>
         </r>
@@ -955,7 +915,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -965,7 +924,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//</t>
         </r>
@@ -974,7 +933,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">经验加成
@@ -985,7 +943,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>402</t>
         </r>
@@ -994,7 +952,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -1004,7 +961,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//</t>
         </r>
@@ -1013,7 +970,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">金币加成
@@ -1024,7 +980,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>403</t>
         </r>
@@ -1033,7 +989,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -1043,7 +998,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//</t>
         </r>
@@ -1052,7 +1007,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">洗炼极品掉落
@@ -1063,7 +1017,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>404</t>
         </r>
@@ -1072,7 +1026,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -1082,7 +1035,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//</t>
         </r>
@@ -1091,7 +1044,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">隐藏属性出现概率
@@ -1102,7 +1054,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>405</t>
         </r>
@@ -1111,7 +1063,6 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -1121,7 +1072,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//</t>
         </r>
@@ -1130,21 +1081,19 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>装备上的宝石槽位出现概率</t>
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="O3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -1153,7 +1102,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -1176,7 +1124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="148">
   <si>
     <t>c</t>
   </si>
@@ -1220,6 +1168,9 @@
     <t>EquipSpaceName</t>
   </si>
   <si>
+    <t>EquipSpaceName_EN</t>
+  </si>
+  <si>
     <t>Icon</t>
   </si>
   <si>
@@ -1262,6 +1213,9 @@
     <t>0级生命石</t>
   </si>
   <si>
+    <t>0-level Life Stone</t>
+  </si>
+  <si>
     <t>xueshi_1</t>
   </si>
   <si>
@@ -1271,6 +1225,9 @@
     <t>1级生命石</t>
   </si>
   <si>
+    <t>1st Level Life Stone</t>
+  </si>
+  <si>
     <t>10000143;200</t>
   </si>
   <si>
@@ -1280,6 +1237,9 @@
     <t>2级生命石</t>
   </si>
   <si>
+    <t>2-level life stone</t>
+  </si>
+  <si>
     <t>10000143;300</t>
   </si>
   <si>
@@ -1289,6 +1249,9 @@
     <t>3级生命石</t>
   </si>
   <si>
+    <t>3rd Level Life Stone</t>
+  </si>
+  <si>
     <t>10000143;400</t>
   </si>
   <si>
@@ -1298,6 +1261,9 @@
     <t>4级生命石</t>
   </si>
   <si>
+    <t>4th-level Life Stone</t>
+  </si>
+  <si>
     <t>10000143;500</t>
   </si>
   <si>
@@ -1307,6 +1273,9 @@
     <t>5级生命石</t>
   </si>
   <si>
+    <t>5th level life stone</t>
+  </si>
+  <si>
     <t>10000152;200</t>
   </si>
   <si>
@@ -1316,6 +1285,9 @@
     <t>6级生命石</t>
   </si>
   <si>
+    <t>6th-level Life Stone</t>
+  </si>
+  <si>
     <t>10000152;300</t>
   </si>
   <si>
@@ -1325,6 +1297,9 @@
     <t>7级生命石</t>
   </si>
   <si>
+    <t>7th Level Life Stone</t>
+  </si>
+  <si>
     <t>10000152;400</t>
   </si>
   <si>
@@ -1334,6 +1309,9 @@
     <t>8级生命石</t>
   </si>
   <si>
+    <t>8th-level Life Stone</t>
+  </si>
+  <si>
     <t>10000152;450</t>
   </si>
   <si>
@@ -1343,6 +1321,9 @@
     <t>9级生命石</t>
   </si>
   <si>
+    <t>9-level Life Stone</t>
+  </si>
+  <si>
     <t>10000152;500</t>
   </si>
   <si>
@@ -1352,182 +1333,254 @@
     <t>10级生命石</t>
   </si>
   <si>
+    <t>10-level Life Stone</t>
+  </si>
+  <si>
     <t>100203;40000</t>
   </si>
   <si>
     <t>0级伤害加成</t>
   </si>
   <si>
+    <t>0-level Damage Bonus</t>
+  </si>
+  <si>
+    <t>qianghua_1</t>
+  </si>
+  <si>
+    <t>10000179;30</t>
+  </si>
+  <si>
     <t>1级伤害加成</t>
   </si>
   <si>
+    <t>Level 1 damage bonus</t>
+  </si>
+  <si>
+    <t>10000179;50</t>
+  </si>
+  <si>
+    <t>200903;0.01</t>
+  </si>
+  <si>
     <t>2级伤害加成</t>
   </si>
   <si>
+    <t>2nd Level Damage Bonus</t>
+  </si>
+  <si>
+    <t>10000179;75</t>
+  </si>
+  <si>
+    <t>200903;0.02</t>
+  </si>
+  <si>
+    <t>3级伤害加成</t>
+  </si>
+  <si>
+    <t>3rd-level damage bonus</t>
+  </si>
+  <si>
+    <t>10000179;100</t>
+  </si>
+  <si>
+    <t>200903;0.03</t>
+  </si>
+  <si>
+    <t>4级伤害加成</t>
+  </si>
+  <si>
+    <t>4th level damage bonus</t>
+  </si>
+  <si>
+    <t>10000179;125</t>
+  </si>
+  <si>
+    <t>200903;0.04</t>
+  </si>
+  <si>
+    <t>5级伤害加成</t>
+  </si>
+  <si>
+    <t>5th level damage increase</t>
+  </si>
+  <si>
+    <t>10000179;150</t>
+  </si>
+  <si>
+    <t>200903;0.05</t>
+  </si>
+  <si>
+    <t>6级伤害加成</t>
+  </si>
+  <si>
+    <t>6th-level damage increase</t>
+  </si>
+  <si>
+    <t>10000179;180</t>
+  </si>
+  <si>
+    <t>200903;0.06</t>
+  </si>
+  <si>
+    <t>7级伤害加成</t>
+  </si>
+  <si>
+    <t>7-level damage bonus</t>
+  </si>
+  <si>
+    <t>10000179;210</t>
+  </si>
+  <si>
+    <t>200903;0.07</t>
+  </si>
+  <si>
+    <t>8级伤害加成</t>
+  </si>
+  <si>
+    <t>8th-level damage bonus</t>
+  </si>
+  <si>
+    <t>10000179;240</t>
+  </si>
+  <si>
+    <t>200903;0.08</t>
+  </si>
+  <si>
+    <t>9级伤害加成</t>
+  </si>
+  <si>
+    <t>9th level damage bonus</t>
+  </si>
+  <si>
+    <t>10000179;270</t>
+  </si>
+  <si>
+    <t>200903;0.09</t>
+  </si>
+  <si>
+    <t>10级伤害加成</t>
+  </si>
+  <si>
+    <t>10-level damage bonus</t>
+  </si>
+  <si>
+    <t>10000179;300</t>
+  </si>
+  <si>
+    <t>200903;0.10</t>
+  </si>
+  <si>
     <t>0级伤害减免</t>
   </si>
   <si>
+    <t>0-level damage reduction</t>
+  </si>
+  <si>
+    <t>qianghua_2</t>
+  </si>
+  <si>
     <t>1级伤害减免</t>
   </si>
   <si>
+    <t>1st level damage reduction</t>
+  </si>
+  <si>
+    <t>201003;0.01</t>
+  </si>
+  <si>
     <t>2级伤害减免</t>
   </si>
   <si>
-    <t>3级伤害加成</t>
-  </si>
-  <si>
-    <t>4级伤害加成</t>
-  </si>
-  <si>
-    <t>5级伤害加成</t>
-  </si>
-  <si>
-    <t>6级伤害加成</t>
-  </si>
-  <si>
-    <t>7级伤害加成</t>
-  </si>
-  <si>
-    <t>8级伤害加成</t>
-  </si>
-  <si>
-    <t>9级伤害加成</t>
-  </si>
-  <si>
-    <t>10级伤害加成</t>
+    <t>2nd level damage reduction</t>
+  </si>
+  <si>
+    <t>201003;0.02</t>
   </si>
   <si>
     <t>3级伤害减免</t>
   </si>
   <si>
+    <t>3rd level damage reduction</t>
+  </si>
+  <si>
+    <t>201003;0.03</t>
+  </si>
+  <si>
     <t>4级伤害减免</t>
   </si>
   <si>
+    <t>4th Level Damage Reduction</t>
+  </si>
+  <si>
+    <t>201003;0.04</t>
+  </si>
+  <si>
     <t>5级伤害减免</t>
   </si>
   <si>
+    <t>5th level damage reduction</t>
+  </si>
+  <si>
+    <t>201003;0.05</t>
+  </si>
+  <si>
     <t>6级伤害减免</t>
   </si>
   <si>
+    <t>6th level damage reduction</t>
+  </si>
+  <si>
+    <t>201003;0.06</t>
+  </si>
+  <si>
     <t>7级伤害减免</t>
   </si>
   <si>
+    <t>7th level damage reduction</t>
+  </si>
+  <si>
+    <t>201003;0.07</t>
+  </si>
+  <si>
     <t>8级伤害减免</t>
   </si>
   <si>
+    <t>8th-level damage reduction</t>
+  </si>
+  <si>
+    <t>201003;0.08</t>
+  </si>
+  <si>
     <t>9级伤害减免</t>
   </si>
   <si>
+    <t>9th level damage reduction</t>
+  </si>
+  <si>
+    <t>201003;0.09</t>
+  </si>
+  <si>
     <t>10级伤害减免</t>
   </si>
   <si>
-    <t>10000179;150</t>
-  </si>
-  <si>
-    <t>10000179;300</t>
-  </si>
-  <si>
-    <t>10000179;30</t>
-  </si>
-  <si>
-    <t>10000179;50</t>
-  </si>
-  <si>
-    <t>10000179;75</t>
-  </si>
-  <si>
-    <t>10000179;100</t>
-  </si>
-  <si>
-    <t>10000179;125</t>
-  </si>
-  <si>
-    <t>10000179;180</t>
-  </si>
-  <si>
-    <t>10000179;210</t>
-  </si>
-  <si>
-    <t>10000179;240</t>
-  </si>
-  <si>
-    <t>10000179;270</t>
-  </si>
-  <si>
-    <t>200903;0.01</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>200903;0.02</t>
-  </si>
-  <si>
-    <t>200903;0.03</t>
-  </si>
-  <si>
-    <t>200903;0.04</t>
-  </si>
-  <si>
-    <t>200903;0.05</t>
-  </si>
-  <si>
-    <t>200903;0.06</t>
-  </si>
-  <si>
-    <t>200903;0.07</t>
-  </si>
-  <si>
-    <t>200903;0.08</t>
-  </si>
-  <si>
-    <t>200903;0.09</t>
-  </si>
-  <si>
-    <t>200903;0.10</t>
-  </si>
-  <si>
-    <t>201003;0.01</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>201003;0.02</t>
-  </si>
-  <si>
-    <t>201003;0.03</t>
-  </si>
-  <si>
-    <t>201003;0.04</t>
-  </si>
-  <si>
-    <t>201003;0.05</t>
-  </si>
-  <si>
-    <t>201003;0.06</t>
-  </si>
-  <si>
-    <t>201003;0.07</t>
-  </si>
-  <si>
-    <t>201003;0.08</t>
-  </si>
-  <si>
-    <t>201003;0.09</t>
+    <t>10% damage reduction at level 10</t>
   </si>
   <si>
     <t>201003;0.10</t>
-  </si>
-  <si>
-    <t>qianghua_1</t>
-  </si>
-  <si>
-    <t>qianghua_2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1538,14 +1591,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1553,49 +1598,207 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1605,18 +1808,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor indexed="13"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="13"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1721,22 +2104,267 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1748,6 +2376,9 @@
     <xf numFmtId="49" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1758,10 +2389,57 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
@@ -1834,9 +2512,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2907,70 +3582,78 @@
       </a:style>
     </a:txDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:N38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C1:O38"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="8.5" style="3" customWidth="1"/>
-    <col min="4" max="5" width="14.125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16" style="3" customWidth="1"/>
-    <col min="7" max="11" width="14.125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="21.875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="24.875" style="3" customWidth="1"/>
-    <col min="14" max="14" width="21.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="27.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16" style="2" customWidth="1"/>
+    <col min="8" max="12" width="14.125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="21.875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="24.875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="21.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:14" s="1" customFormat="1" ht="14.25"/>
-    <row r="2" spans="3:14" ht="13.5" customHeight="1">
-      <c r="D2" s="3" t="s">
+    <row r="1" s="1" customFormat="1" ht="14.25"/>
+    <row r="2" customHeight="1" spans="4:5">
+      <c r="D2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
+    <row r="3" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C4" s="4" t="s">
+    <row r="4" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -2979,1333 +3662,1437 @@
       <c r="E4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="7" t="s">
         <v>23</v>
       </c>
+      <c r="O4" s="7" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="5" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C5" s="4" t="s">
-        <v>24</v>
+    <row r="5" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C5" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="6" t="s">
+      <c r="I5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>26</v>
       </c>
+      <c r="O5" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="6" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C6" s="7">
+    <row r="6" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C6" s="8">
         <v>10100</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="10">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="E6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="12">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8">
         <v>10101</v>
       </c>
-      <c r="H6" s="11">
-        <v>0</v>
-      </c>
-      <c r="I6" s="11">
+      <c r="I6" s="13">
+        <v>0</v>
+      </c>
+      <c r="J6" s="13">
         <v>60</v>
       </c>
-      <c r="J6" s="11">
-        <v>1</v>
-      </c>
-      <c r="K6" s="11">
+      <c r="K6" s="13">
+        <v>1</v>
+      </c>
+      <c r="L6" s="13">
         <v>25000000</v>
       </c>
-      <c r="L6" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="11">
-        <v>0</v>
-      </c>
-      <c r="N6" s="10">
+      <c r="M6" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="13">
+        <v>0</v>
+      </c>
+      <c r="O6" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C7" s="7">
+    <row r="7" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C7" s="8">
         <v>10101</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="10">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7">
+      <c r="G7" s="12">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8">
         <v>10102</v>
       </c>
-      <c r="H7" s="11">
-        <v>1</v>
-      </c>
-      <c r="I7" s="11">
+      <c r="I7" s="13">
+        <v>1</v>
+      </c>
+      <c r="J7" s="13">
         <v>60</v>
       </c>
-      <c r="J7" s="11">
-        <v>1</v>
-      </c>
-      <c r="K7" s="11">
+      <c r="K7" s="13">
+        <v>1</v>
+      </c>
+      <c r="L7" s="13">
         <v>50000000</v>
       </c>
-      <c r="L7" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="N7" s="10">
+      <c r="M7" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="O7" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C8" s="7">
+    <row r="8" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C8" s="8">
         <v>10102</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="10">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7">
+      <c r="D8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="12">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8">
         <v>10103</v>
       </c>
-      <c r="H8" s="11">
+      <c r="I8" s="13">
         <v>2</v>
       </c>
-      <c r="I8" s="11">
+      <c r="J8" s="13">
         <v>60</v>
       </c>
-      <c r="J8" s="11">
-        <v>1</v>
-      </c>
-      <c r="K8" s="11">
+      <c r="K8" s="13">
+        <v>1</v>
+      </c>
+      <c r="L8" s="13">
         <v>75000000</v>
       </c>
-      <c r="L8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N8" s="10">
+      <c r="M8" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="O8" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:14" ht="19.5" customHeight="1">
-      <c r="C9" s="7">
+    <row r="9" ht="19.5" customHeight="1" spans="3:15">
+      <c r="C9" s="8">
         <v>10103</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="10">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7">
+      <c r="D9" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="12">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8">
         <v>10104</v>
       </c>
-      <c r="H9" s="11">
+      <c r="I9" s="13">
         <v>3</v>
       </c>
-      <c r="I9" s="11">
+      <c r="J9" s="13">
         <v>60</v>
       </c>
-      <c r="J9" s="11">
-        <v>1</v>
-      </c>
-      <c r="K9" s="11">
+      <c r="K9" s="13">
+        <v>1</v>
+      </c>
+      <c r="L9" s="13">
         <v>100000000</v>
       </c>
-      <c r="L9" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N9" s="10">
+      <c r="M9" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="O9" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:14" ht="19.5" customHeight="1">
-      <c r="C10" s="7">
+    <row r="10" ht="19.5" customHeight="1" spans="3:15">
+      <c r="C10" s="8">
         <v>10104</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7">
+      <c r="D10" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="12">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8">
         <v>10105</v>
       </c>
-      <c r="H10" s="11">
+      <c r="I10" s="13">
         <v>4</v>
       </c>
-      <c r="I10" s="11">
+      <c r="J10" s="13">
         <v>60</v>
       </c>
-      <c r="J10" s="11">
-        <v>1</v>
-      </c>
-      <c r="K10" s="11">
+      <c r="K10" s="13">
+        <v>1</v>
+      </c>
+      <c r="L10" s="13">
         <v>125000000</v>
       </c>
-      <c r="L10" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="N10" s="10">
+      <c r="M10" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="O10" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:14" ht="19.5" customHeight="1">
-      <c r="C11" s="7">
+    <row r="11" ht="19.5" customHeight="1" spans="3:15">
+      <c r="C11" s="8">
         <v>10105</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="10">
-        <v>1</v>
-      </c>
-      <c r="G11" s="7">
+      <c r="D11" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="12">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8">
         <v>10106</v>
       </c>
-      <c r="H11" s="11">
+      <c r="I11" s="13">
         <v>5</v>
       </c>
-      <c r="I11" s="11">
+      <c r="J11" s="13">
         <v>60</v>
       </c>
-      <c r="J11" s="11">
-        <v>1</v>
-      </c>
-      <c r="K11" s="11">
+      <c r="K11" s="13">
+        <v>1</v>
+      </c>
+      <c r="L11" s="13">
         <v>150000000</v>
       </c>
-      <c r="L11" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="N11" s="10">
+      <c r="M11" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="O11" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="3:14" ht="19.5" customHeight="1">
-      <c r="C12" s="7">
+    <row r="12" ht="19.5" customHeight="1" spans="3:15">
+      <c r="C12" s="8">
         <v>10106</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="10">
-        <v>1</v>
-      </c>
-      <c r="G12" s="7">
+      <c r="D12" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="12">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8">
         <v>10107</v>
       </c>
-      <c r="H12" s="11">
+      <c r="I12" s="13">
         <v>6</v>
       </c>
-      <c r="I12" s="11">
+      <c r="J12" s="13">
         <v>60</v>
       </c>
-      <c r="J12" s="11">
-        <v>1</v>
-      </c>
-      <c r="K12" s="11">
+      <c r="K12" s="13">
+        <v>1</v>
+      </c>
+      <c r="L12" s="13">
         <v>175000000</v>
       </c>
-      <c r="L12" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="N12" s="10">
+      <c r="M12" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C13" s="7">
+    <row r="13" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C13" s="8">
         <v>10107</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="10">
-        <v>1</v>
-      </c>
-      <c r="G13" s="7">
+      <c r="D13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="12">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8">
         <v>10108</v>
       </c>
-      <c r="H13" s="11">
+      <c r="I13" s="13">
         <v>7</v>
       </c>
-      <c r="I13" s="11">
+      <c r="J13" s="13">
         <v>60</v>
       </c>
-      <c r="J13" s="11">
-        <v>1</v>
-      </c>
-      <c r="K13" s="11">
+      <c r="K13" s="13">
+        <v>1</v>
+      </c>
+      <c r="L13" s="13">
         <v>200000000</v>
       </c>
-      <c r="L13" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="N13" s="10">
+      <c r="M13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="O13" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C14" s="7">
+    <row r="14" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C14" s="8">
         <v>10108</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="10">
-        <v>1</v>
-      </c>
-      <c r="G14" s="7">
+      <c r="D14" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="12">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8">
         <v>10109</v>
       </c>
-      <c r="H14" s="11">
+      <c r="I14" s="13">
         <v>8</v>
       </c>
-      <c r="I14" s="11">
+      <c r="J14" s="13">
         <v>60</v>
       </c>
-      <c r="J14" s="11">
-        <v>1</v>
-      </c>
-      <c r="K14" s="11">
+      <c r="K14" s="13">
+        <v>1</v>
+      </c>
+      <c r="L14" s="13">
         <v>250000000</v>
       </c>
-      <c r="L14" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="N14" s="10">
+      <c r="M14" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="O14" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C15" s="7">
+    <row r="15" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C15" s="8">
         <v>10109</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="10">
-        <v>1</v>
-      </c>
-      <c r="G15" s="7">
+      <c r="D15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="12">
+        <v>1</v>
+      </c>
+      <c r="H15" s="8">
         <v>10110</v>
       </c>
-      <c r="H15" s="11">
+      <c r="I15" s="13">
         <v>9</v>
       </c>
-      <c r="I15" s="11">
+      <c r="J15" s="13">
         <v>60</v>
       </c>
-      <c r="J15" s="11">
-        <v>1</v>
-      </c>
-      <c r="K15" s="11">
+      <c r="K15" s="13">
+        <v>1</v>
+      </c>
+      <c r="L15" s="13">
         <v>300000000</v>
       </c>
-      <c r="L15" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N15" s="10">
+      <c r="M15" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="O15" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C16" s="7">
+    <row r="16" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C16" s="8">
         <v>10110</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="10">
-        <v>1</v>
-      </c>
-      <c r="G16" s="7">
-        <v>0</v>
-      </c>
-      <c r="H16" s="11">
+      <c r="D16" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="12">
+        <v>1</v>
+      </c>
+      <c r="H16" s="8">
+        <v>0</v>
+      </c>
+      <c r="I16" s="13">
         <v>10</v>
       </c>
-      <c r="I16" s="11">
+      <c r="J16" s="13">
         <v>60</v>
       </c>
-      <c r="J16" s="11">
-        <v>1</v>
-      </c>
-      <c r="K16" s="11">
+      <c r="K16" s="13">
+        <v>1</v>
+      </c>
+      <c r="L16" s="13">
         <v>300000000</v>
       </c>
-      <c r="L16" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="N16" s="10">
+      <c r="M16" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="O16" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C17" s="7">
+    <row r="17" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C17" s="8">
         <v>20100</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="9" t="s">
+      <c r="D17" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="12">
+        <v>1</v>
+      </c>
+      <c r="H17" s="8">
+        <v>20101</v>
+      </c>
+      <c r="I17" s="13">
+        <v>0</v>
+      </c>
+      <c r="J17" s="13">
+        <v>60</v>
+      </c>
+      <c r="K17" s="13">
+        <v>1</v>
+      </c>
+      <c r="L17" s="13">
+        <v>0</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="N17" s="13">
+        <v>0</v>
+      </c>
+      <c r="O17" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C18" s="8">
+        <v>20101</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="12">
+        <v>1</v>
+      </c>
+      <c r="H18" s="8">
+        <v>20102</v>
+      </c>
+      <c r="I18" s="13">
+        <v>1</v>
+      </c>
+      <c r="J18" s="13">
+        <v>60</v>
+      </c>
+      <c r="K18" s="13">
+        <v>1</v>
+      </c>
+      <c r="L18" s="13">
+        <v>0</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="O18" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C19" s="8">
+        <v>20102</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="12">
+        <v>1</v>
+      </c>
+      <c r="H19" s="8">
+        <v>20103</v>
+      </c>
+      <c r="I19" s="13">
+        <v>2</v>
+      </c>
+      <c r="J19" s="13">
+        <v>60</v>
+      </c>
+      <c r="K19" s="13">
+        <v>1</v>
+      </c>
+      <c r="L19" s="13">
+        <v>0</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="O19" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C20" s="8">
+        <v>20103</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G20" s="12">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8">
+        <v>20104</v>
+      </c>
+      <c r="I20" s="13">
+        <v>1</v>
+      </c>
+      <c r="J20" s="13">
+        <v>60</v>
+      </c>
+      <c r="K20" s="13">
+        <v>1</v>
+      </c>
+      <c r="L20" s="13">
+        <v>0</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="O20" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C21" s="8">
+        <v>20104</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="12">
+        <v>1</v>
+      </c>
+      <c r="H21" s="8">
+        <v>20105</v>
+      </c>
+      <c r="I21" s="13">
+        <v>2</v>
+      </c>
+      <c r="J21" s="13">
+        <v>60</v>
+      </c>
+      <c r="K21" s="13">
+        <v>1</v>
+      </c>
+      <c r="L21" s="13">
+        <v>0</v>
+      </c>
+      <c r="M21" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="O21" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C22" s="8">
+        <v>20105</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" s="12">
+        <v>1</v>
+      </c>
+      <c r="H22" s="8">
+        <v>20106</v>
+      </c>
+      <c r="I22" s="13">
+        <v>1</v>
+      </c>
+      <c r="J22" s="13">
+        <v>60</v>
+      </c>
+      <c r="K22" s="13">
+        <v>1</v>
+      </c>
+      <c r="L22" s="13">
+        <v>0</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="O22" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C23" s="8">
+        <v>20106</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="12">
+        <v>1</v>
+      </c>
+      <c r="H23" s="8">
+        <v>20107</v>
+      </c>
+      <c r="I23" s="13">
+        <v>2</v>
+      </c>
+      <c r="J23" s="13">
+        <v>60</v>
+      </c>
+      <c r="K23" s="13">
+        <v>1</v>
+      </c>
+      <c r="L23" s="13">
+        <v>0</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="N23" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="O23" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C24" s="8">
+        <v>20107</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24" s="12">
+        <v>1</v>
+      </c>
+      <c r="H24" s="8">
+        <v>20108</v>
+      </c>
+      <c r="I24" s="13">
+        <v>1</v>
+      </c>
+      <c r="J24" s="13">
+        <v>60</v>
+      </c>
+      <c r="K24" s="13">
+        <v>1</v>
+      </c>
+      <c r="L24" s="13">
+        <v>0</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="O24" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C25" s="8">
+        <v>20108</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G25" s="12">
+        <v>1</v>
+      </c>
+      <c r="H25" s="8">
+        <v>20109</v>
+      </c>
+      <c r="I25" s="13">
+        <v>2</v>
+      </c>
+      <c r="J25" s="13">
+        <v>60</v>
+      </c>
+      <c r="K25" s="13">
+        <v>1</v>
+      </c>
+      <c r="L25" s="13">
+        <v>0</v>
+      </c>
+      <c r="M25" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="N25" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="O25" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C26" s="8">
+        <v>20109</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" s="12">
+        <v>1</v>
+      </c>
+      <c r="H26" s="8">
+        <v>20110</v>
+      </c>
+      <c r="I26" s="13">
+        <v>1</v>
+      </c>
+      <c r="J26" s="13">
+        <v>60</v>
+      </c>
+      <c r="K26" s="13">
+        <v>1</v>
+      </c>
+      <c r="L26" s="13">
+        <v>0</v>
+      </c>
+      <c r="M26" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="N26" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="O26" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C27" s="8">
+        <v>20110</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="F17" s="10">
-        <v>1</v>
-      </c>
-      <c r="G17" s="7">
-        <v>20101</v>
-      </c>
-      <c r="H17" s="11">
-        <v>0</v>
-      </c>
-      <c r="I17" s="11">
+      <c r="F27" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G27" s="12">
+        <v>1</v>
+      </c>
+      <c r="H27" s="8">
+        <v>0</v>
+      </c>
+      <c r="I27" s="13">
+        <v>2</v>
+      </c>
+      <c r="J27" s="13">
         <v>60</v>
       </c>
-      <c r="J17" s="11">
-        <v>1</v>
-      </c>
-      <c r="K17" s="11">
-        <v>0</v>
-      </c>
-      <c r="L17" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="M17" s="11">
-        <v>0</v>
-      </c>
-      <c r="N17" s="10">
+      <c r="K27" s="13">
+        <v>1</v>
+      </c>
+      <c r="L27" s="13">
+        <v>0</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="O27" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C18" s="7">
-        <v>20101</v>
-      </c>
-      <c r="D18" s="8" t="s">
+    <row r="28" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C28" s="8">
+        <v>30100</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G28" s="12">
+        <v>1</v>
+      </c>
+      <c r="H28" s="8">
+        <v>30101</v>
+      </c>
+      <c r="I28" s="13">
+        <v>0</v>
+      </c>
+      <c r="J28" s="13">
         <v>60</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F18" s="10">
-        <v>1</v>
-      </c>
-      <c r="G18" s="7">
-        <v>20102</v>
-      </c>
-      <c r="H18" s="11">
-        <v>1</v>
-      </c>
-      <c r="I18" s="11">
+      <c r="K28" s="13">
+        <v>1</v>
+      </c>
+      <c r="L28" s="13">
+        <v>0</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="N28" s="13">
+        <v>0</v>
+      </c>
+      <c r="O28" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C29" s="8">
+        <v>30101</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" s="12">
+        <v>1</v>
+      </c>
+      <c r="H29" s="8">
+        <v>30102</v>
+      </c>
+      <c r="I29" s="13">
+        <v>1</v>
+      </c>
+      <c r="J29" s="13">
         <v>60</v>
       </c>
-      <c r="J18" s="11">
-        <v>1</v>
-      </c>
-      <c r="K18" s="11">
-        <v>0</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="N18" s="10">
+      <c r="K29" s="13">
+        <v>1</v>
+      </c>
+      <c r="L29" s="13">
+        <v>0</v>
+      </c>
+      <c r="M29" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="N29" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="O29" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C19" s="7">
-        <v>20102</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F19" s="10">
-        <v>1</v>
-      </c>
-      <c r="G19" s="7">
-        <v>20103</v>
-      </c>
-      <c r="H19" s="11">
+    <row r="30" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C30" s="8">
+        <v>30102</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G30" s="12">
+        <v>1</v>
+      </c>
+      <c r="H30" s="8">
+        <v>30103</v>
+      </c>
+      <c r="I30" s="13">
         <v>2</v>
       </c>
-      <c r="I19" s="11">
+      <c r="J30" s="13">
         <v>60</v>
       </c>
-      <c r="J19" s="11">
-        <v>1</v>
-      </c>
-      <c r="K19" s="11">
-        <v>0</v>
-      </c>
-      <c r="L19" s="11" t="s">
+      <c r="K30" s="13">
+        <v>1</v>
+      </c>
+      <c r="L30" s="13">
+        <v>0</v>
+      </c>
+      <c r="M30" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="N30" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="O30" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C31" s="8">
+        <v>30103</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G31" s="12">
+        <v>1</v>
+      </c>
+      <c r="H31" s="8">
+        <v>30104</v>
+      </c>
+      <c r="I31" s="13">
+        <v>1</v>
+      </c>
+      <c r="J31" s="13">
+        <v>60</v>
+      </c>
+      <c r="K31" s="13">
+        <v>1</v>
+      </c>
+      <c r="L31" s="13">
+        <v>0</v>
+      </c>
+      <c r="M31" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="M19" s="11" t="s">
+      <c r="N31" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="O31" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C32" s="8">
+        <v>30104</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G32" s="12">
+        <v>1</v>
+      </c>
+      <c r="H32" s="8">
+        <v>30105</v>
+      </c>
+      <c r="I32" s="13">
+        <v>2</v>
+      </c>
+      <c r="J32" s="13">
+        <v>60</v>
+      </c>
+      <c r="K32" s="13">
+        <v>1</v>
+      </c>
+      <c r="L32" s="13">
+        <v>0</v>
+      </c>
+      <c r="M32" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="N32" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="O32" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C33" s="8">
+        <v>30105</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G33" s="12">
+        <v>1</v>
+      </c>
+      <c r="H33" s="8">
+        <v>30106</v>
+      </c>
+      <c r="I33" s="13">
+        <v>1</v>
+      </c>
+      <c r="J33" s="13">
+        <v>60</v>
+      </c>
+      <c r="K33" s="13">
+        <v>1</v>
+      </c>
+      <c r="L33" s="13">
+        <v>0</v>
+      </c>
+      <c r="M33" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N33" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="O33" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C20" s="7">
-        <v>20103</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F20" s="10">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7">
-        <v>20104</v>
-      </c>
-      <c r="H20" s="11">
-        <v>1</v>
-      </c>
-      <c r="I20" s="11">
+    <row r="34" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C34" s="8">
+        <v>30106</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G34" s="12">
+        <v>1</v>
+      </c>
+      <c r="H34" s="8">
+        <v>30107</v>
+      </c>
+      <c r="I34" s="13">
+        <v>2</v>
+      </c>
+      <c r="J34" s="13">
         <v>60</v>
       </c>
-      <c r="J20" s="11">
-        <v>1</v>
-      </c>
-      <c r="K20" s="11">
-        <v>0</v>
-      </c>
-      <c r="L20" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="N20" s="10">
+      <c r="K34" s="13">
+        <v>1</v>
+      </c>
+      <c r="L34" s="13">
+        <v>0</v>
+      </c>
+      <c r="M34" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="N34" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="O34" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C21" s="7">
-        <v>20104</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F21" s="10">
-        <v>1</v>
-      </c>
-      <c r="G21" s="7">
-        <v>20105</v>
-      </c>
-      <c r="H21" s="11">
+    <row r="35" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C35" s="8">
+        <v>30107</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G35" s="12">
+        <v>1</v>
+      </c>
+      <c r="H35" s="8">
+        <v>30108</v>
+      </c>
+      <c r="I35" s="13">
+        <v>1</v>
+      </c>
+      <c r="J35" s="13">
+        <v>60</v>
+      </c>
+      <c r="K35" s="13">
+        <v>1</v>
+      </c>
+      <c r="L35" s="13">
+        <v>0</v>
+      </c>
+      <c r="M35" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="N35" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="O35" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C36" s="8">
+        <v>30108</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G36" s="12">
+        <v>1</v>
+      </c>
+      <c r="H36" s="8">
+        <v>30109</v>
+      </c>
+      <c r="I36" s="13">
         <v>2</v>
       </c>
-      <c r="I21" s="11">
+      <c r="J36" s="13">
         <v>60</v>
       </c>
-      <c r="J21" s="11">
-        <v>1</v>
-      </c>
-      <c r="K21" s="11">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="N21" s="10">
+      <c r="K36" s="13">
+        <v>1</v>
+      </c>
+      <c r="L36" s="13">
+        <v>0</v>
+      </c>
+      <c r="M36" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="N36" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="O36" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C22" s="7">
-        <v>20105</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F22" s="10">
-        <v>1</v>
-      </c>
-      <c r="G22" s="7">
-        <v>20106</v>
-      </c>
-      <c r="H22" s="11">
-        <v>1</v>
-      </c>
-      <c r="I22" s="11">
+    <row r="37" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C37" s="8">
+        <v>30109</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G37" s="12">
+        <v>1</v>
+      </c>
+      <c r="H37" s="8">
+        <v>30110</v>
+      </c>
+      <c r="I37" s="13">
+        <v>1</v>
+      </c>
+      <c r="J37" s="13">
         <v>60</v>
       </c>
-      <c r="J22" s="11">
-        <v>1</v>
-      </c>
-      <c r="K22" s="11">
-        <v>0</v>
-      </c>
-      <c r="L22" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="N22" s="10">
+      <c r="K37" s="13">
+        <v>1</v>
+      </c>
+      <c r="L37" s="13">
+        <v>0</v>
+      </c>
+      <c r="M37" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="N37" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="O37" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C23" s="7">
-        <v>20106</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F23" s="10">
-        <v>1</v>
-      </c>
-      <c r="G23" s="7">
-        <v>20107</v>
-      </c>
-      <c r="H23" s="11">
+    <row r="38" ht="20.1" customHeight="1" spans="3:15">
+      <c r="C38" s="8">
+        <v>30110</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G38" s="12">
+        <v>1</v>
+      </c>
+      <c r="H38" s="8">
+        <v>0</v>
+      </c>
+      <c r="I38" s="13">
         <v>2</v>
       </c>
-      <c r="I23" s="11">
+      <c r="J38" s="13">
         <v>60</v>
       </c>
-      <c r="J23" s="11">
-        <v>1</v>
-      </c>
-      <c r="K23" s="11">
-        <v>0</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="N23" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C24" s="7">
-        <v>20107</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F24" s="10">
-        <v>1</v>
-      </c>
-      <c r="G24" s="7">
-        <v>20108</v>
-      </c>
-      <c r="H24" s="11">
-        <v>1</v>
-      </c>
-      <c r="I24" s="11">
-        <v>60</v>
-      </c>
-      <c r="J24" s="11">
-        <v>1</v>
-      </c>
-      <c r="K24" s="11">
-        <v>0</v>
-      </c>
-      <c r="L24" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="M24" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="N24" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C25" s="7">
-        <v>20108</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F25" s="10">
-        <v>1</v>
-      </c>
-      <c r="G25" s="7">
-        <v>20109</v>
-      </c>
-      <c r="H25" s="11">
-        <v>2</v>
-      </c>
-      <c r="I25" s="11">
-        <v>60</v>
-      </c>
-      <c r="J25" s="11">
-        <v>1</v>
-      </c>
-      <c r="K25" s="11">
-        <v>0</v>
-      </c>
-      <c r="L25" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="M25" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="N25" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C26" s="7">
-        <v>20109</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26" s="10">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7">
-        <v>20110</v>
-      </c>
-      <c r="H26" s="11">
-        <v>1</v>
-      </c>
-      <c r="I26" s="11">
-        <v>60</v>
-      </c>
-      <c r="J26" s="11">
-        <v>1</v>
-      </c>
-      <c r="K26" s="11">
-        <v>0</v>
-      </c>
-      <c r="L26" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="M26" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="N26" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C27" s="7">
-        <v>20110</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F27" s="10">
-        <v>1</v>
-      </c>
-      <c r="G27" s="7">
-        <v>0</v>
-      </c>
-      <c r="H27" s="11">
-        <v>2</v>
-      </c>
-      <c r="I27" s="11">
-        <v>60</v>
-      </c>
-      <c r="J27" s="11">
-        <v>1</v>
-      </c>
-      <c r="K27" s="11">
-        <v>0</v>
-      </c>
-      <c r="L27" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="N27" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C28" s="7">
-        <v>30100</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E28" s="9" t="s">
+      <c r="K38" s="13">
+        <v>1</v>
+      </c>
+      <c r="L38" s="13">
+        <v>0</v>
+      </c>
+      <c r="M38" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="F28" s="10">
-        <v>1</v>
-      </c>
-      <c r="G28" s="7">
-        <v>30101</v>
-      </c>
-      <c r="H28" s="11">
-        <v>0</v>
-      </c>
-      <c r="I28" s="11">
-        <v>60</v>
-      </c>
-      <c r="J28" s="11">
-        <v>1</v>
-      </c>
-      <c r="K28" s="11">
-        <v>0</v>
-      </c>
-      <c r="L28" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="M28" s="11">
-        <v>0</v>
-      </c>
-      <c r="N28" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C29" s="7">
-        <v>30101</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F29" s="10">
-        <v>1</v>
-      </c>
-      <c r="G29" s="7">
-        <v>30102</v>
-      </c>
-      <c r="H29" s="11">
-        <v>1</v>
-      </c>
-      <c r="I29" s="11">
-        <v>60</v>
-      </c>
-      <c r="J29" s="11">
-        <v>1</v>
-      </c>
-      <c r="K29" s="11">
-        <v>0</v>
-      </c>
-      <c r="L29" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="M29" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="N29" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C30" s="7">
-        <v>30102</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F30" s="10">
-        <v>1</v>
-      </c>
-      <c r="G30" s="7">
-        <v>30103</v>
-      </c>
-      <c r="H30" s="11">
-        <v>2</v>
-      </c>
-      <c r="I30" s="11">
-        <v>60</v>
-      </c>
-      <c r="J30" s="11">
-        <v>1</v>
-      </c>
-      <c r="K30" s="11">
-        <v>0</v>
-      </c>
-      <c r="L30" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="M30" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="N30" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C31" s="7">
-        <v>30103</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F31" s="10">
-        <v>1</v>
-      </c>
-      <c r="G31" s="7">
-        <v>30104</v>
-      </c>
-      <c r="H31" s="11">
-        <v>1</v>
-      </c>
-      <c r="I31" s="11">
-        <v>60</v>
-      </c>
-      <c r="J31" s="11">
-        <v>1</v>
-      </c>
-      <c r="K31" s="11">
-        <v>0</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="M31" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="N31" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C32" s="7">
-        <v>30104</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F32" s="10">
-        <v>1</v>
-      </c>
-      <c r="G32" s="7">
-        <v>30105</v>
-      </c>
-      <c r="H32" s="11">
-        <v>2</v>
-      </c>
-      <c r="I32" s="11">
-        <v>60</v>
-      </c>
-      <c r="J32" s="11">
-        <v>1</v>
-      </c>
-      <c r="K32" s="11">
-        <v>0</v>
-      </c>
-      <c r="L32" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="M32" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="N32" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C33" s="7">
-        <v>30105</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F33" s="10">
-        <v>1</v>
-      </c>
-      <c r="G33" s="7">
-        <v>30106</v>
-      </c>
-      <c r="H33" s="11">
-        <v>1</v>
-      </c>
-      <c r="I33" s="11">
-        <v>60</v>
-      </c>
-      <c r="J33" s="11">
-        <v>1</v>
-      </c>
-      <c r="K33" s="11">
-        <v>0</v>
-      </c>
-      <c r="L33" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="M33" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="N33" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C34" s="7">
-        <v>30106</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F34" s="10">
-        <v>1</v>
-      </c>
-      <c r="G34" s="7">
-        <v>30107</v>
-      </c>
-      <c r="H34" s="11">
-        <v>2</v>
-      </c>
-      <c r="I34" s="11">
-        <v>60</v>
-      </c>
-      <c r="J34" s="11">
-        <v>1</v>
-      </c>
-      <c r="K34" s="11">
-        <v>0</v>
-      </c>
-      <c r="L34" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="M34" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="N34" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C35" s="7">
-        <v>30107</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F35" s="10">
-        <v>1</v>
-      </c>
-      <c r="G35" s="7">
-        <v>30108</v>
-      </c>
-      <c r="H35" s="11">
-        <v>1</v>
-      </c>
-      <c r="I35" s="11">
-        <v>60</v>
-      </c>
-      <c r="J35" s="11">
-        <v>1</v>
-      </c>
-      <c r="K35" s="11">
-        <v>0</v>
-      </c>
-      <c r="L35" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="M35" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="N35" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C36" s="7">
-        <v>30108</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F36" s="10">
-        <v>1</v>
-      </c>
-      <c r="G36" s="7">
-        <v>30109</v>
-      </c>
-      <c r="H36" s="11">
-        <v>2</v>
-      </c>
-      <c r="I36" s="11">
-        <v>60</v>
-      </c>
-      <c r="J36" s="11">
-        <v>1</v>
-      </c>
-      <c r="K36" s="11">
-        <v>0</v>
-      </c>
-      <c r="L36" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="M36" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="N36" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C37" s="7">
-        <v>30109</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F37" s="10">
-        <v>1</v>
-      </c>
-      <c r="G37" s="7">
-        <v>30110</v>
-      </c>
-      <c r="H37" s="11">
-        <v>1</v>
-      </c>
-      <c r="I37" s="11">
-        <v>60</v>
-      </c>
-      <c r="J37" s="11">
-        <v>1</v>
-      </c>
-      <c r="K37" s="11">
-        <v>0</v>
-      </c>
-      <c r="L37" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="M37" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="N37" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="3:14" ht="20.100000000000001" customHeight="1">
-      <c r="C38" s="7">
-        <v>30110</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F38" s="10">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7">
-        <v>0</v>
-      </c>
-      <c r="H38" s="11">
-        <v>2</v>
-      </c>
-      <c r="I38" s="11">
-        <v>60</v>
-      </c>
-      <c r="J38" s="11">
-        <v>1</v>
-      </c>
-      <c r="K38" s="11">
-        <v>0</v>
-      </c>
-      <c r="L38" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="M38" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="N38" s="10">
+      <c r="N38" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="O38" s="12">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/PublicQiangHuaConfig.xlsx
+++ b/Excel/PublicQiangHuaConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F5FDC7-22E9-4F2A-B0C0-4BB926692C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12795"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipQiangHuaProto" sheetId="1" r:id="rId1"/>
@@ -27,19 +33,20 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Admin</author>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="G3" authorId="0">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -48,6 +55,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -56,13 +64,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="1">
+    <comment ref="N3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者</t>
@@ -72,7 +81,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>:
 10.</t>
@@ -82,6 +91,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">生命值
@@ -92,7 +102,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>11.</t>
         </r>
@@ -101,6 +111,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>物理攻击</t>
@@ -110,7 +121,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">       
 14.</t>
@@ -120,6 +131,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">魔法攻击
@@ -130,7 +142,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>17.</t>
         </r>
@@ -139,6 +151,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>物理防御</t>
@@ -148,7 +161,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">        
 20.</t>
@@ -158,6 +171,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">魔法防御
@@ -168,7 +182,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>30.</t>
         </r>
@@ -177,6 +191,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">暴击
@@ -187,7 +202,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>31.</t>
         </r>
@@ -196,6 +211,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">命中
@@ -206,7 +222,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>32.</t>
         </r>
@@ -215,6 +231,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">闪避
@@ -225,7 +242,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>33.</t>
         </r>
@@ -234,6 +251,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">物理免伤
@@ -244,7 +262,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>34.</t>
         </r>
@@ -253,6 +271,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">魔法免伤
@@ -263,7 +282,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>35.</t>
         </r>
@@ -272,6 +291,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">移动速度
@@ -282,7 +302,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>36.</t>
         </r>
@@ -291,6 +311,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">伤害减免
@@ -301,7 +322,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>50:</t>
         </r>
@@ -310,6 +331,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">血量百分比
@@ -320,7 +342,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>51</t>
         </r>
@@ -329,6 +351,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：物攻百分比
@@ -339,7 +362,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>52</t>
         </r>
@@ -348,6 +371,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：魔攻百分比
@@ -358,7 +382,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>53</t>
         </r>
@@ -367,6 +391,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：物防百分比
@@ -377,7 +402,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>54</t>
         </r>
@@ -386,6 +411,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：魔防百分比
@@ -396,7 +422,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>101</t>
         </r>
@@ -405,6 +431,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：格挡值
@@ -415,7 +442,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>111</t>
         </r>
@@ -424,6 +451,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：重击概率
@@ -434,7 +462,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">112:  </t>
         </r>
@@ -443,6 +471,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">重击附加伤害值
@@ -453,7 +482,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">121:  </t>
         </r>
@@ -462,6 +491,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">每次普通攻击附加的伤害值
@@ -472,7 +502,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">131:  </t>
         </r>
@@ -481,6 +511,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>忽视目标防御值</t>
@@ -490,7 +521,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">   
 132:  </t>
@@ -500,6 +531,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">忽视目标魔防值
@@ -510,7 +542,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">133:  </t>
         </r>
@@ -519,6 +551,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">忽视目标百分比防御值
@@ -529,7 +562,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">134:  </t>
         </r>
@@ -538,6 +571,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">忽视目标百分比魔防值
@@ -548,7 +582,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">141:  </t>
         </r>
@@ -557,6 +591,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">吸血概率
@@ -567,7 +602,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">151:  </t>
         </r>
@@ -576,6 +611,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">法术反击
@@ -586,7 +622,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">152:  </t>
         </r>
@@ -595,6 +631,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">攻击反击
@@ -605,7 +642,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>161</t>
         </r>
@@ -614,6 +651,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：韧性
@@ -624,7 +662,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>201</t>
         </r>
@@ -633,6 +671,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：初始暴击等级
@@ -643,7 +682,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>202</t>
         </r>
@@ -652,6 +691,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：初始韧性等级
@@ -662,7 +702,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>203</t>
         </r>
@@ -671,6 +711,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：初始命中等级
@@ -681,7 +722,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>204</t>
         </r>
@@ -690,6 +731,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">：初始闪避等级
@@ -700,7 +742,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>301:</t>
         </r>
@@ -709,6 +751,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">光抗性
@@ -719,7 +762,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>302:</t>
         </r>
@@ -728,6 +771,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">暗抗性
@@ -738,7 +782,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>303:</t>
         </r>
@@ -747,6 +791,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">火抗性
@@ -757,7 +802,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>304:</t>
         </r>
@@ -766,6 +811,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">水抗性
@@ -776,7 +822,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>305:</t>
         </r>
@@ -785,6 +831,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">电抗性
@@ -795,7 +842,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>321</t>
         </r>
@@ -804,6 +851,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -813,7 +861,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//</t>
         </r>
@@ -822,6 +870,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">野兽攻击抗性
@@ -832,7 +881,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>322</t>
         </r>
@@ -841,6 +890,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -850,7 +900,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//</t>
         </r>
@@ -859,6 +909,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">人物攻击抗性
@@ -869,7 +920,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>323</t>
         </r>
@@ -878,6 +929,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -887,7 +939,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//</t>
         </r>
@@ -896,6 +948,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">恶魔攻击抗性
@@ -906,7 +959,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>401</t>
         </r>
@@ -915,6 +968,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -924,7 +978,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//</t>
         </r>
@@ -933,6 +987,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">经验加成
@@ -943,7 +998,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>402</t>
         </r>
@@ -952,6 +1007,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -961,7 +1017,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//</t>
         </r>
@@ -970,6 +1026,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">金币加成
@@ -980,7 +1037,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>403</t>
         </r>
@@ -989,6 +1046,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -998,7 +1056,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//</t>
         </r>
@@ -1007,6 +1065,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">洗炼极品掉落
@@ -1017,7 +1076,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>404</t>
         </r>
@@ -1026,6 +1085,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -1035,7 +1095,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//</t>
         </r>
@@ -1044,6 +1104,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">隐藏属性出现概率
@@ -1054,7 +1115,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>405</t>
         </r>
@@ -1063,6 +1124,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>：</t>
@@ -1072,7 +1134,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//</t>
         </r>
@@ -1081,19 +1143,21 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>装备上的宝石槽位出现概率</t>
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="0">
+    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -1102,6 +1166,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -1573,14 +1638,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="29">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1591,6 +1650,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1598,196 +1658,51 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1812,194 +1727,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="16">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2104,253 +1833,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2364,16 +1851,10 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2389,57 +1870,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
@@ -2512,6 +1946,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3582,12 +3019,12 @@
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C1:O38"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
@@ -3602,8 +3039,8 @@
     <col min="15" max="15" width="21.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25"/>
-    <row r="2" customHeight="1" spans="4:5">
+    <row r="1" spans="3:15" s="1" customFormat="1" ht="14.25"/>
+    <row r="2" spans="3:15" ht="13.5" customHeight="1">
       <c r="D2" s="2" t="s">
         <v>0</v>
       </c>
@@ -3611,7 +3048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="3:15">
+    <row r="3" spans="3:15" ht="20.100000000000001" customHeight="1">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -3652,7 +3089,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:15">
+    <row r="4" spans="3:15" ht="20.100000000000001" customHeight="1">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -3662,38 +3099,38 @@
       <c r="E4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:15">
+    <row r="5" spans="3:15" ht="20.100000000000001" customHeight="1">
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
@@ -3703,1396 +3140,1397 @@
       <c r="E5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C6" s="8">
+    <row r="6" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C6" s="7">
         <v>10100</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="12">
-        <v>1</v>
-      </c>
-      <c r="H6" s="8">
+      <c r="G6" s="10">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
         <v>10101</v>
       </c>
-      <c r="I6" s="13">
-        <v>0</v>
-      </c>
-      <c r="J6" s="13">
+      <c r="I6" s="11">
+        <v>0</v>
+      </c>
+      <c r="J6" s="11">
         <v>60</v>
       </c>
-      <c r="K6" s="13">
-        <v>1</v>
-      </c>
-      <c r="L6" s="13">
+      <c r="K6" s="11">
+        <v>1</v>
+      </c>
+      <c r="L6" s="11">
         <v>25000000</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="N6" s="13">
-        <v>0</v>
-      </c>
-      <c r="O6" s="12">
+      <c r="N6" s="11">
+        <v>0</v>
+      </c>
+      <c r="O6" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C7" s="8">
+    <row r="7" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C7" s="7">
         <v>10101</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="12">
-        <v>1</v>
-      </c>
-      <c r="H7" s="8">
+      <c r="G7" s="10">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7">
         <v>10102</v>
       </c>
-      <c r="I7" s="13">
-        <v>1</v>
-      </c>
-      <c r="J7" s="13">
+      <c r="I7" s="11">
+        <v>1</v>
+      </c>
+      <c r="J7" s="11">
         <v>60</v>
       </c>
-      <c r="K7" s="13">
-        <v>1</v>
-      </c>
-      <c r="L7" s="13">
+      <c r="K7" s="11">
+        <v>1</v>
+      </c>
+      <c r="L7" s="11">
         <v>50000000</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="M7" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="N7" s="13" t="s">
+      <c r="N7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="O7" s="12">
+      <c r="O7" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C8" s="8">
+    <row r="8" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C8" s="7">
         <v>10102</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="12">
-        <v>1</v>
-      </c>
-      <c r="H8" s="8">
+      <c r="G8" s="10">
+        <v>1</v>
+      </c>
+      <c r="H8" s="7">
         <v>10103</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="11">
         <v>2</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="11">
         <v>60</v>
       </c>
-      <c r="K8" s="13">
-        <v>1</v>
-      </c>
-      <c r="L8" s="13">
+      <c r="K8" s="11">
+        <v>1</v>
+      </c>
+      <c r="L8" s="11">
         <v>75000000</v>
       </c>
-      <c r="M8" s="14" t="s">
+      <c r="M8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="N8" s="13" t="s">
+      <c r="N8" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="O8" s="12">
+      <c r="O8" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="19.5" customHeight="1" spans="3:15">
-      <c r="C9" s="8">
+    <row r="9" spans="3:15" ht="19.5" customHeight="1">
+      <c r="C9" s="7">
         <v>10103</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="12">
-        <v>1</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="G9" s="10">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7">
         <v>10104</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="11">
         <v>3</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="11">
         <v>60</v>
       </c>
-      <c r="K9" s="13">
-        <v>1</v>
-      </c>
-      <c r="L9" s="13">
+      <c r="K9" s="11">
+        <v>1</v>
+      </c>
+      <c r="L9" s="11">
         <v>100000000</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="M9" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="N9" s="13" t="s">
+      <c r="N9" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="O9" s="12">
+      <c r="O9" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="19.5" customHeight="1" spans="3:15">
-      <c r="C10" s="8">
+    <row r="10" spans="3:15" ht="19.5" customHeight="1">
+      <c r="C10" s="7">
         <v>10104</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="12">
-        <v>1</v>
-      </c>
-      <c r="H10" s="8">
+      <c r="G10" s="10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7">
         <v>10105</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="11">
         <v>4</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="11">
         <v>60</v>
       </c>
-      <c r="K10" s="13">
-        <v>1</v>
-      </c>
-      <c r="L10" s="13">
+      <c r="K10" s="11">
+        <v>1</v>
+      </c>
+      <c r="L10" s="11">
         <v>125000000</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="M10" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="N10" s="13" t="s">
+      <c r="N10" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="O10" s="12">
+      <c r="O10" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="19.5" customHeight="1" spans="3:15">
-      <c r="C11" s="8">
+    <row r="11" spans="3:15" ht="19.5" customHeight="1">
+      <c r="C11" s="7">
         <v>10105</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="12">
-        <v>1</v>
-      </c>
-      <c r="H11" s="8">
+      <c r="G11" s="10">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7">
         <v>10106</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="11">
         <v>5</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="11">
         <v>60</v>
       </c>
-      <c r="K11" s="13">
-        <v>1</v>
-      </c>
-      <c r="L11" s="13">
+      <c r="K11" s="11">
+        <v>1</v>
+      </c>
+      <c r="L11" s="11">
         <v>150000000</v>
       </c>
-      <c r="M11" s="14" t="s">
+      <c r="M11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="N11" s="13" t="s">
+      <c r="N11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1" spans="3:15">
-      <c r="C12" s="8">
+    <row r="12" spans="3:15" ht="19.5" customHeight="1">
+      <c r="C12" s="7">
         <v>10106</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="12">
-        <v>1</v>
-      </c>
-      <c r="H12" s="8">
+      <c r="G12" s="10">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7">
         <v>10107</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="11">
         <v>6</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="11">
         <v>60</v>
       </c>
-      <c r="K12" s="13">
-        <v>1</v>
-      </c>
-      <c r="L12" s="13">
+      <c r="K12" s="11">
+        <v>1</v>
+      </c>
+      <c r="L12" s="11">
         <v>175000000</v>
       </c>
-      <c r="M12" s="14" t="s">
+      <c r="M12" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="N12" s="13" t="s">
+      <c r="N12" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="O12" s="12">
+      <c r="O12" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C13" s="8">
+    <row r="13" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C13" s="7">
         <v>10107</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="12">
-        <v>1</v>
-      </c>
-      <c r="H13" s="8">
+      <c r="G13" s="10">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7">
         <v>10108</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="11">
         <v>7</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="11">
         <v>60</v>
       </c>
-      <c r="K13" s="13">
-        <v>1</v>
-      </c>
-      <c r="L13" s="13">
+      <c r="K13" s="11">
+        <v>1</v>
+      </c>
+      <c r="L13" s="11">
         <v>200000000</v>
       </c>
-      <c r="M13" s="14" t="s">
+      <c r="M13" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="N13" s="13" t="s">
+      <c r="N13" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="O13" s="12">
+      <c r="O13" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C14" s="8">
+    <row r="14" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C14" s="7">
         <v>10108</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="12">
-        <v>1</v>
-      </c>
-      <c r="H14" s="8">
+      <c r="G14" s="10">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7">
         <v>10109</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="11">
         <v>8</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="11">
         <v>60</v>
       </c>
-      <c r="K14" s="13">
-        <v>1</v>
-      </c>
-      <c r="L14" s="13">
+      <c r="K14" s="11">
+        <v>1</v>
+      </c>
+      <c r="L14" s="11">
         <v>250000000</v>
       </c>
-      <c r="M14" s="14" t="s">
+      <c r="M14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="N14" s="13" t="s">
+      <c r="N14" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="O14" s="12">
+      <c r="O14" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C15" s="8">
+    <row r="15" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C15" s="7">
         <v>10109</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="12">
-        <v>1</v>
-      </c>
-      <c r="H15" s="8">
+      <c r="G15" s="10">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7">
         <v>10110</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="11">
         <v>9</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="11">
         <v>60</v>
       </c>
-      <c r="K15" s="13">
-        <v>1</v>
-      </c>
-      <c r="L15" s="13">
+      <c r="K15" s="11">
+        <v>1</v>
+      </c>
+      <c r="L15" s="11">
         <v>300000000</v>
       </c>
-      <c r="M15" s="14" t="s">
+      <c r="M15" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="N15" s="13" t="s">
+      <c r="N15" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="O15" s="12">
+      <c r="O15" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C16" s="8">
+    <row r="16" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C16" s="7">
         <v>10110</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="12">
-        <v>1</v>
-      </c>
-      <c r="H16" s="8">
-        <v>0</v>
-      </c>
-      <c r="I16" s="13">
+      <c r="G16" s="10">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7">
+        <v>0</v>
+      </c>
+      <c r="I16" s="11">
         <v>10</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="11">
         <v>60</v>
       </c>
-      <c r="K16" s="13">
-        <v>1</v>
-      </c>
-      <c r="L16" s="13">
+      <c r="K16" s="11">
+        <v>1</v>
+      </c>
+      <c r="L16" s="11">
         <v>300000000</v>
       </c>
-      <c r="M16" s="14" t="s">
+      <c r="M16" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="N16" s="13" t="s">
+      <c r="N16" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="O16" s="12">
+      <c r="O16" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C17" s="8">
+    <row r="17" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C17" s="7">
         <v>20100</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G17" s="12">
-        <v>1</v>
-      </c>
-      <c r="H17" s="8">
+      <c r="G17" s="10">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7">
         <v>20101</v>
       </c>
-      <c r="I17" s="13">
-        <v>0</v>
-      </c>
-      <c r="J17" s="13">
+      <c r="I17" s="11">
+        <v>0</v>
+      </c>
+      <c r="J17" s="11">
         <v>60</v>
       </c>
-      <c r="K17" s="13">
-        <v>1</v>
-      </c>
-      <c r="L17" s="13">
-        <v>0</v>
-      </c>
-      <c r="M17" s="13" t="s">
+      <c r="K17" s="11">
+        <v>1</v>
+      </c>
+      <c r="L17" s="11">
+        <v>0</v>
+      </c>
+      <c r="M17" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="N17" s="13">
-        <v>0</v>
-      </c>
-      <c r="O17" s="12">
+      <c r="N17" s="11">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C18" s="8">
+    <row r="18" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C18" s="7">
         <v>20101</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G18" s="12">
-        <v>1</v>
-      </c>
-      <c r="H18" s="8">
+      <c r="G18" s="10">
+        <v>1</v>
+      </c>
+      <c r="H18" s="7">
         <v>20102</v>
       </c>
-      <c r="I18" s="13">
-        <v>1</v>
-      </c>
-      <c r="J18" s="13">
+      <c r="I18" s="11">
+        <v>1</v>
+      </c>
+      <c r="J18" s="11">
         <v>60</v>
       </c>
-      <c r="K18" s="13">
-        <v>1</v>
-      </c>
-      <c r="L18" s="13">
-        <v>0</v>
-      </c>
-      <c r="M18" s="13" t="s">
+      <c r="K18" s="11">
+        <v>1</v>
+      </c>
+      <c r="L18" s="11">
+        <v>0</v>
+      </c>
+      <c r="M18" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="N18" s="13" t="s">
+      <c r="N18" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="O18" s="12">
+      <c r="O18" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C19" s="8">
+    <row r="19" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C19" s="7">
         <v>20102</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G19" s="12">
-        <v>1</v>
-      </c>
-      <c r="H19" s="8">
+      <c r="G19" s="10">
+        <v>1</v>
+      </c>
+      <c r="H19" s="7">
         <v>20103</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="11">
         <v>2</v>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="11">
         <v>60</v>
       </c>
-      <c r="K19" s="13">
-        <v>1</v>
-      </c>
-      <c r="L19" s="13">
-        <v>0</v>
-      </c>
-      <c r="M19" s="13" t="s">
+      <c r="K19" s="11">
+        <v>1</v>
+      </c>
+      <c r="L19" s="11">
+        <v>0</v>
+      </c>
+      <c r="M19" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="N19" s="13" t="s">
+      <c r="N19" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="O19" s="12">
+      <c r="O19" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C20" s="8">
+    <row r="20" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C20" s="7">
         <v>20103</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G20" s="12">
-        <v>1</v>
-      </c>
-      <c r="H20" s="8">
+      <c r="G20" s="10">
+        <v>1</v>
+      </c>
+      <c r="H20" s="7">
         <v>20104</v>
       </c>
-      <c r="I20" s="13">
-        <v>1</v>
-      </c>
-      <c r="J20" s="13">
+      <c r="I20" s="11">
+        <v>1</v>
+      </c>
+      <c r="J20" s="11">
         <v>60</v>
       </c>
-      <c r="K20" s="13">
-        <v>1</v>
-      </c>
-      <c r="L20" s="13">
-        <v>0</v>
-      </c>
-      <c r="M20" s="13" t="s">
+      <c r="K20" s="11">
+        <v>1</v>
+      </c>
+      <c r="L20" s="11">
+        <v>0</v>
+      </c>
+      <c r="M20" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="N20" s="13" t="s">
+      <c r="N20" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="O20" s="12">
+      <c r="O20" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C21" s="8">
+    <row r="21" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C21" s="7">
         <v>20104</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G21" s="12">
-        <v>1</v>
-      </c>
-      <c r="H21" s="8">
+      <c r="G21" s="10">
+        <v>1</v>
+      </c>
+      <c r="H21" s="7">
         <v>20105</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="11">
         <v>2</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="11">
         <v>60</v>
       </c>
-      <c r="K21" s="13">
-        <v>1</v>
-      </c>
-      <c r="L21" s="13">
-        <v>0</v>
-      </c>
-      <c r="M21" s="13" t="s">
+      <c r="K21" s="11">
+        <v>1</v>
+      </c>
+      <c r="L21" s="11">
+        <v>0</v>
+      </c>
+      <c r="M21" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="N21" s="13" t="s">
+      <c r="N21" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="O21" s="12">
+      <c r="O21" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C22" s="8">
+    <row r="22" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C22" s="7">
         <v>20105</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="12">
-        <v>1</v>
-      </c>
-      <c r="H22" s="8">
+      <c r="G22" s="10">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7">
         <v>20106</v>
       </c>
-      <c r="I22" s="13">
-        <v>1</v>
-      </c>
-      <c r="J22" s="13">
+      <c r="I22" s="11">
+        <v>1</v>
+      </c>
+      <c r="J22" s="11">
         <v>60</v>
       </c>
-      <c r="K22" s="13">
-        <v>1</v>
-      </c>
-      <c r="L22" s="13">
-        <v>0</v>
-      </c>
-      <c r="M22" s="13" t="s">
+      <c r="K22" s="11">
+        <v>1</v>
+      </c>
+      <c r="L22" s="11">
+        <v>0</v>
+      </c>
+      <c r="M22" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="N22" s="13" t="s">
+      <c r="N22" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="O22" s="12">
+      <c r="O22" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C23" s="8">
+    <row r="23" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C23" s="7">
         <v>20106</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G23" s="12">
-        <v>1</v>
-      </c>
-      <c r="H23" s="8">
+      <c r="G23" s="10">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7">
         <v>20107</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="11">
         <v>2</v>
       </c>
-      <c r="J23" s="13">
+      <c r="J23" s="11">
         <v>60</v>
       </c>
-      <c r="K23" s="13">
-        <v>1</v>
-      </c>
-      <c r="L23" s="13">
-        <v>0</v>
-      </c>
-      <c r="M23" s="13" t="s">
+      <c r="K23" s="11">
+        <v>1</v>
+      </c>
+      <c r="L23" s="11">
+        <v>0</v>
+      </c>
+      <c r="M23" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="N23" s="13" t="s">
+      <c r="N23" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="O23" s="12">
+      <c r="O23" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C24" s="8">
+    <row r="24" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C24" s="7">
         <v>20107</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G24" s="12">
-        <v>1</v>
-      </c>
-      <c r="H24" s="8">
+      <c r="G24" s="10">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7">
         <v>20108</v>
       </c>
-      <c r="I24" s="13">
-        <v>1</v>
-      </c>
-      <c r="J24" s="13">
+      <c r="I24" s="11">
+        <v>1</v>
+      </c>
+      <c r="J24" s="11">
         <v>60</v>
       </c>
-      <c r="K24" s="13">
-        <v>1</v>
-      </c>
-      <c r="L24" s="13">
-        <v>0</v>
-      </c>
-      <c r="M24" s="13" t="s">
+      <c r="K24" s="11">
+        <v>1</v>
+      </c>
+      <c r="L24" s="11">
+        <v>0</v>
+      </c>
+      <c r="M24" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="N24" s="13" t="s">
+      <c r="N24" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="O24" s="12">
+      <c r="O24" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C25" s="8">
+    <row r="25" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C25" s="7">
         <v>20108</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G25" s="12">
-        <v>1</v>
-      </c>
-      <c r="H25" s="8">
+      <c r="G25" s="10">
+        <v>1</v>
+      </c>
+      <c r="H25" s="7">
         <v>20109</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="11">
         <v>2</v>
       </c>
-      <c r="J25" s="13">
+      <c r="J25" s="11">
         <v>60</v>
       </c>
-      <c r="K25" s="13">
-        <v>1</v>
-      </c>
-      <c r="L25" s="13">
-        <v>0</v>
-      </c>
-      <c r="M25" s="13" t="s">
+      <c r="K25" s="11">
+        <v>1</v>
+      </c>
+      <c r="L25" s="11">
+        <v>0</v>
+      </c>
+      <c r="M25" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="N25" s="13" t="s">
+      <c r="N25" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="O25" s="12">
+      <c r="O25" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C26" s="8">
+    <row r="26" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C26" s="7">
         <v>20109</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="12">
-        <v>1</v>
-      </c>
-      <c r="H26" s="8">
+      <c r="G26" s="10">
+        <v>1</v>
+      </c>
+      <c r="H26" s="7">
         <v>20110</v>
       </c>
-      <c r="I26" s="13">
-        <v>1</v>
-      </c>
-      <c r="J26" s="13">
+      <c r="I26" s="11">
+        <v>1</v>
+      </c>
+      <c r="J26" s="11">
         <v>60</v>
       </c>
-      <c r="K26" s="13">
-        <v>1</v>
-      </c>
-      <c r="L26" s="13">
-        <v>0</v>
-      </c>
-      <c r="M26" s="13" t="s">
+      <c r="K26" s="11">
+        <v>1</v>
+      </c>
+      <c r="L26" s="11">
+        <v>0</v>
+      </c>
+      <c r="M26" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="N26" s="13" t="s">
+      <c r="N26" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="O26" s="12">
+      <c r="O26" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C27" s="8">
+    <row r="27" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C27" s="7">
         <v>20110</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G27" s="12">
-        <v>1</v>
-      </c>
-      <c r="H27" s="8">
-        <v>0</v>
-      </c>
-      <c r="I27" s="13">
+      <c r="G27" s="10">
+        <v>1</v>
+      </c>
+      <c r="H27" s="7">
+        <v>0</v>
+      </c>
+      <c r="I27" s="11">
         <v>2</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="11">
         <v>60</v>
       </c>
-      <c r="K27" s="13">
-        <v>1</v>
-      </c>
-      <c r="L27" s="13">
-        <v>0</v>
-      </c>
-      <c r="M27" s="13" t="s">
+      <c r="K27" s="11">
+        <v>1</v>
+      </c>
+      <c r="L27" s="11">
+        <v>0</v>
+      </c>
+      <c r="M27" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="N27" s="13" t="s">
+      <c r="N27" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="O27" s="12">
+      <c r="O27" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C28" s="8">
+    <row r="28" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C28" s="7">
         <v>30100</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G28" s="12">
-        <v>1</v>
-      </c>
-      <c r="H28" s="8">
+      <c r="G28" s="10">
+        <v>1</v>
+      </c>
+      <c r="H28" s="7">
         <v>30101</v>
       </c>
-      <c r="I28" s="13">
-        <v>0</v>
-      </c>
-      <c r="J28" s="13">
+      <c r="I28" s="11">
+        <v>0</v>
+      </c>
+      <c r="J28" s="11">
         <v>60</v>
       </c>
-      <c r="K28" s="13">
-        <v>1</v>
-      </c>
-      <c r="L28" s="13">
-        <v>0</v>
-      </c>
-      <c r="M28" s="14" t="s">
+      <c r="K28" s="11">
+        <v>1</v>
+      </c>
+      <c r="L28" s="11">
+        <v>0</v>
+      </c>
+      <c r="M28" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="N28" s="13">
-        <v>0</v>
-      </c>
-      <c r="O28" s="12">
+      <c r="N28" s="11">
+        <v>0</v>
+      </c>
+      <c r="O28" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C29" s="8">
+    <row r="29" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C29" s="7">
         <v>30101</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G29" s="12">
-        <v>1</v>
-      </c>
-      <c r="H29" s="8">
+      <c r="G29" s="10">
+        <v>1</v>
+      </c>
+      <c r="H29" s="7">
         <v>30102</v>
       </c>
-      <c r="I29" s="13">
-        <v>1</v>
-      </c>
-      <c r="J29" s="13">
+      <c r="I29" s="11">
+        <v>1</v>
+      </c>
+      <c r="J29" s="11">
         <v>60</v>
       </c>
-      <c r="K29" s="13">
-        <v>1</v>
-      </c>
-      <c r="L29" s="13">
-        <v>0</v>
-      </c>
-      <c r="M29" s="14" t="s">
+      <c r="K29" s="11">
+        <v>1</v>
+      </c>
+      <c r="L29" s="11">
+        <v>0</v>
+      </c>
+      <c r="M29" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="N29" s="13" t="s">
+      <c r="N29" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="O29" s="12">
+      <c r="O29" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C30" s="8">
+    <row r="30" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C30" s="7">
         <v>30102</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G30" s="12">
-        <v>1</v>
-      </c>
-      <c r="H30" s="8">
+      <c r="G30" s="10">
+        <v>1</v>
+      </c>
+      <c r="H30" s="7">
         <v>30103</v>
       </c>
-      <c r="I30" s="13">
+      <c r="I30" s="11">
         <v>2</v>
       </c>
-      <c r="J30" s="13">
+      <c r="J30" s="11">
         <v>60</v>
       </c>
-      <c r="K30" s="13">
-        <v>1</v>
-      </c>
-      <c r="L30" s="13">
-        <v>0</v>
-      </c>
-      <c r="M30" s="14" t="s">
+      <c r="K30" s="11">
+        <v>1</v>
+      </c>
+      <c r="L30" s="11">
+        <v>0</v>
+      </c>
+      <c r="M30" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="N30" s="13" t="s">
+      <c r="N30" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="O30" s="12">
+      <c r="O30" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C31" s="8">
+    <row r="31" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C31" s="7">
         <v>30103</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G31" s="12">
-        <v>1</v>
-      </c>
-      <c r="H31" s="8">
+      <c r="G31" s="10">
+        <v>1</v>
+      </c>
+      <c r="H31" s="7">
         <v>30104</v>
       </c>
-      <c r="I31" s="13">
-        <v>1</v>
-      </c>
-      <c r="J31" s="13">
+      <c r="I31" s="11">
+        <v>1</v>
+      </c>
+      <c r="J31" s="11">
         <v>60</v>
       </c>
-      <c r="K31" s="13">
-        <v>1</v>
-      </c>
-      <c r="L31" s="13">
-        <v>0</v>
-      </c>
-      <c r="M31" s="14" t="s">
+      <c r="K31" s="11">
+        <v>1</v>
+      </c>
+      <c r="L31" s="11">
+        <v>0</v>
+      </c>
+      <c r="M31" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="N31" s="13" t="s">
+      <c r="N31" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="O31" s="12">
+      <c r="O31" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C32" s="8">
+    <row r="32" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C32" s="7">
         <v>30104</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G32" s="12">
-        <v>1</v>
-      </c>
-      <c r="H32" s="8">
+      <c r="G32" s="10">
+        <v>1</v>
+      </c>
+      <c r="H32" s="7">
         <v>30105</v>
       </c>
-      <c r="I32" s="13">
+      <c r="I32" s="11">
         <v>2</v>
       </c>
-      <c r="J32" s="13">
+      <c r="J32" s="11">
         <v>60</v>
       </c>
-      <c r="K32" s="13">
-        <v>1</v>
-      </c>
-      <c r="L32" s="13">
-        <v>0</v>
-      </c>
-      <c r="M32" s="14" t="s">
+      <c r="K32" s="11">
+        <v>1</v>
+      </c>
+      <c r="L32" s="11">
+        <v>0</v>
+      </c>
+      <c r="M32" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="N32" s="13" t="s">
+      <c r="N32" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="O32" s="12">
+      <c r="O32" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C33" s="8">
+    <row r="33" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C33" s="7">
         <v>30105</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G33" s="12">
-        <v>1</v>
-      </c>
-      <c r="H33" s="8">
+      <c r="G33" s="10">
+        <v>1</v>
+      </c>
+      <c r="H33" s="7">
         <v>30106</v>
       </c>
-      <c r="I33" s="13">
-        <v>1</v>
-      </c>
-      <c r="J33" s="13">
+      <c r="I33" s="11">
+        <v>1</v>
+      </c>
+      <c r="J33" s="11">
         <v>60</v>
       </c>
-      <c r="K33" s="13">
-        <v>1</v>
-      </c>
-      <c r="L33" s="13">
-        <v>0</v>
-      </c>
-      <c r="M33" s="14" t="s">
+      <c r="K33" s="11">
+        <v>1</v>
+      </c>
+      <c r="L33" s="11">
+        <v>0</v>
+      </c>
+      <c r="M33" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="N33" s="13" t="s">
+      <c r="N33" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="O33" s="12">
+      <c r="O33" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C34" s="8">
+    <row r="34" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C34" s="7">
         <v>30106</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G34" s="12">
-        <v>1</v>
-      </c>
-      <c r="H34" s="8">
+      <c r="G34" s="10">
+        <v>1</v>
+      </c>
+      <c r="H34" s="7">
         <v>30107</v>
       </c>
-      <c r="I34" s="13">
+      <c r="I34" s="11">
         <v>2</v>
       </c>
-      <c r="J34" s="13">
+      <c r="J34" s="11">
         <v>60</v>
       </c>
-      <c r="K34" s="13">
-        <v>1</v>
-      </c>
-      <c r="L34" s="13">
-        <v>0</v>
-      </c>
-      <c r="M34" s="14" t="s">
+      <c r="K34" s="11">
+        <v>1</v>
+      </c>
+      <c r="L34" s="11">
+        <v>0</v>
+      </c>
+      <c r="M34" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="N34" s="13" t="s">
+      <c r="N34" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="O34" s="12">
+      <c r="O34" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C35" s="8">
+    <row r="35" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C35" s="7">
         <v>30107</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G35" s="12">
-        <v>1</v>
-      </c>
-      <c r="H35" s="8">
+      <c r="G35" s="10">
+        <v>1</v>
+      </c>
+      <c r="H35" s="7">
         <v>30108</v>
       </c>
-      <c r="I35" s="13">
-        <v>1</v>
-      </c>
-      <c r="J35" s="13">
+      <c r="I35" s="11">
+        <v>1</v>
+      </c>
+      <c r="J35" s="11">
         <v>60</v>
       </c>
-      <c r="K35" s="13">
-        <v>1</v>
-      </c>
-      <c r="L35" s="13">
-        <v>0</v>
-      </c>
-      <c r="M35" s="14" t="s">
+      <c r="K35" s="11">
+        <v>1</v>
+      </c>
+      <c r="L35" s="11">
+        <v>0</v>
+      </c>
+      <c r="M35" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="N35" s="13" t="s">
+      <c r="N35" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="O35" s="12">
+      <c r="O35" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="36" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C36" s="8">
+    <row r="36" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C36" s="7">
         <v>30108</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G36" s="12">
-        <v>1</v>
-      </c>
-      <c r="H36" s="8">
+      <c r="G36" s="10">
+        <v>1</v>
+      </c>
+      <c r="H36" s="7">
         <v>30109</v>
       </c>
-      <c r="I36" s="13">
+      <c r="I36" s="11">
         <v>2</v>
       </c>
-      <c r="J36" s="13">
+      <c r="J36" s="11">
         <v>60</v>
       </c>
-      <c r="K36" s="13">
-        <v>1</v>
-      </c>
-      <c r="L36" s="13">
-        <v>0</v>
-      </c>
-      <c r="M36" s="14" t="s">
+      <c r="K36" s="11">
+        <v>1</v>
+      </c>
+      <c r="L36" s="11">
+        <v>0</v>
+      </c>
+      <c r="M36" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="N36" s="13" t="s">
+      <c r="N36" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="O36" s="12">
+      <c r="O36" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="37" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C37" s="8">
+    <row r="37" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C37" s="7">
         <v>30109</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G37" s="12">
-        <v>1</v>
-      </c>
-      <c r="H37" s="8">
+      <c r="G37" s="10">
+        <v>1</v>
+      </c>
+      <c r="H37" s="7">
         <v>30110</v>
       </c>
-      <c r="I37" s="13">
-        <v>1</v>
-      </c>
-      <c r="J37" s="13">
+      <c r="I37" s="11">
+        <v>1</v>
+      </c>
+      <c r="J37" s="11">
         <v>60</v>
       </c>
-      <c r="K37" s="13">
-        <v>1</v>
-      </c>
-      <c r="L37" s="13">
-        <v>0</v>
-      </c>
-      <c r="M37" s="14" t="s">
+      <c r="K37" s="11">
+        <v>1</v>
+      </c>
+      <c r="L37" s="11">
+        <v>0</v>
+      </c>
+      <c r="M37" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="N37" s="13" t="s">
+      <c r="N37" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="O37" s="12">
+      <c r="O37" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="38" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C38" s="8">
+    <row r="38" spans="3:15" ht="20.100000000000001" customHeight="1">
+      <c r="C38" s="7">
         <v>30110</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G38" s="12">
-        <v>1</v>
-      </c>
-      <c r="H38" s="8">
-        <v>0</v>
-      </c>
-      <c r="I38" s="13">
+      <c r="G38" s="10">
+        <v>1</v>
+      </c>
+      <c r="H38" s="7">
+        <v>0</v>
+      </c>
+      <c r="I38" s="11">
         <v>2</v>
       </c>
-      <c r="J38" s="13">
+      <c r="J38" s="11">
         <v>60</v>
       </c>
-      <c r="K38" s="13">
-        <v>1</v>
-      </c>
-      <c r="L38" s="13">
-        <v>0</v>
-      </c>
-      <c r="M38" s="14" t="s">
+      <c r="K38" s="11">
+        <v>1</v>
+      </c>
+      <c r="L38" s="11">
+        <v>0</v>
+      </c>
+      <c r="M38" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="N38" s="13" t="s">
+      <c r="N38" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="O38" s="12">
+      <c r="O38" s="10">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>